--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486514_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486514_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9769</v>
+        <v>1.9075</v>
       </c>
       <c r="E2" t="n">
-        <v>4.182</v>
+        <v>3.9585</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2051</v>
+        <v>-2.051</v>
       </c>
       <c r="G2" t="n">
         <v>3.3691</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0857</v>
+        <v>-1.1551</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0036</v>
+        <v>-0.2199</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0893</v>
+        <v>-0.9352</v>
       </c>
       <c r="V2" t="n">
         <v>0.9986</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DOMENECH FONTANA</t>
+          <t>K. WEBSTER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7739</v>
+        <v>1.7485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4672</v>
+        <v>1.3871</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3067</v>
+        <v>0.3614</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.598</v>
+        <v>4.0122</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1161</v>
+        <v>-0.3099</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7141</v>
+        <v>4.3222</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.5364</v>
+        <v>5.2524</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8828</v>
+        <v>0.8704</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.4193</v>
+        <v>4.382</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0616</v>
+        <v>-1.2401</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7668</v>
+        <v>-1.1803</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7052</v>
+        <v>-0.0598</v>
       </c>
       <c r="P3" t="n">
-        <v>1.305</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.3501</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0669</v>
+        <v>0.0856</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8736</v>
+        <v>0.2896</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1932</v>
+        <v>-0.204</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.0432</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.13</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. WEBSTER</t>
+          <t>J. LOPEZ SANTANA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6934</v>
+        <v>1.3896</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4245</v>
+        <v>3.0731</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2689</v>
+        <v>-1.6835</v>
       </c>
       <c r="G4" t="n">
-        <v>4.0122</v>
+        <v>3.3374</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3099</v>
+        <v>0.3253</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3222</v>
+        <v>3.0121</v>
       </c>
       <c r="J4" t="n">
-        <v>5.2524</v>
+        <v>3.7815</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8704</v>
+        <v>1.3901</v>
       </c>
       <c r="L4" t="n">
-        <v>4.382</v>
+        <v>2.3914</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2401</v>
+        <v>-0.4441</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1803</v>
+        <v>-1.0648</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0598</v>
+        <v>0.6207</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.3926</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.3501</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9694</v>
+        <v>-0.3182</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6729000000000001</v>
+        <v>0.1839</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2965</v>
+        <v>-0.502</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0432</v>
+        <v>-2.0647</v>
       </c>
       <c r="W4" t="n">
         <v>0.1952</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.152</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SVEJCAR</t>
+          <t>A. DOMENECH FONTANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4806</v>
+        <v>0.249</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1404</v>
+        <v>0.3122</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6599</v>
+        <v>-0.06320000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3744</v>
+        <v>-1.598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2098</v>
+        <v>1.1161</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.5842</v>
+        <v>-2.7141</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5327</v>
+        <v>-1.5364</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8426</v>
+        <v>1.8828</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3754</v>
+        <v>-3.4193</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8417</v>
+        <v>-0.0616</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6328</v>
+        <v>-0.7668</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2088</v>
+        <v>0.7052</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6455</v>
+        <v>0.542</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5432</v>
+        <v>0.7186</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1887</v>
+        <v>-0.1767</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9779</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.152</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. FAVERANI TATSCH</t>
+          <t>S. SVEJCAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2288</v>
+        <v>0.0566</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1149</v>
+        <v>0.4699</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8862</v>
+        <v>-0.4133</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2038</v>
+        <v>-1.3744</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1428</v>
+        <v>0.2098</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3466</v>
+        <v>-1.5842</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6798</v>
+        <v>-0.5327</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1045</v>
+        <v>0.8426</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5754</v>
+        <v>-1.3754</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.476</v>
+        <v>-0.8417</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2473</v>
+        <v>-0.6328</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2287</v>
+        <v>-0.2088</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>1.5225</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1751</v>
+        <v>1.5225</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2418</v>
+        <v>-1.0695</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2197</v>
+        <v>-0.1274</v>
       </c>
       <c r="U6" t="n">
-        <v>1.022</v>
+        <v>-0.9421</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.2168</v>
+        <v>0.9779</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6072</v>
+        <v>-0.152</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LOPEZ SANTANA</t>
+          <t>I. RIVERA CARROLL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09950000000000001</v>
+        <v>-0.367</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9987</v>
+        <v>-0.4393</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.8993</v>
+        <v>0.0723</v>
       </c>
       <c r="G7" t="n">
-        <v>3.3374</v>
+        <v>0.6863</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3253</v>
+        <v>0.2433</v>
       </c>
       <c r="I7" t="n">
-        <v>3.0121</v>
+        <v>0.443</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7815</v>
+        <v>0.9222</v>
       </c>
       <c r="K7" t="n">
-        <v>1.3901</v>
+        <v>0.3102</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3914</v>
+        <v>0.612</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4441</v>
+        <v>-0.2359</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0648</v>
+        <v>-0.067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6207</v>
+        <v>-0.1689</v>
       </c>
       <c r="P7" t="n">
-        <v>0.435</v>
+        <v>-0.87</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.6082</v>
+        <v>-0.1833</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8904</v>
+        <v>-0.274</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7178</v>
+        <v>0.0907</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.0647</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. RIVERA CARROLL</t>
+          <t>A. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4286</v>
+        <v>-1.1221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4393</v>
+        <v>-0.759</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0107</v>
+        <v>-0.3631</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6863</v>
+        <v>-1.1915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2433</v>
+        <v>-1.107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.443</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9222</v>
+        <v>-0.7086</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3102</v>
+        <v>-0.7086</v>
       </c>
       <c r="L8" t="n">
-        <v>0.612</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2359</v>
+        <v>-0.4829</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.067</v>
+        <v>-0.3985</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1689</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2449</v>
+        <v>-0.1481</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0291</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. HARGUINDEY MANEIRO</t>
+          <t>V. FAVERANI TATSCH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3764</v>
+        <v>-1.2556</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9825</v>
+        <v>0.4011</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3939</v>
+        <v>-1.6567</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1915</v>
+        <v>0.2038</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.107</v>
+        <v>-0.1428</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.3466</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7086</v>
+        <v>1.6798</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7086</v>
+        <v>1.1045</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.5754</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4829</v>
+        <v>-1.476</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3985</v>
+        <v>-1.2473</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.2287</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2175</v>
+        <v>2.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4024</v>
+        <v>0.7574</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.274</v>
+        <v>0.5059</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>0.2514</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.2168</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.6072</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0489</v>
+        <v>-2.0382</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3966</v>
+        <v>-0.6634</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6523</v>
+        <v>-1.3749</v>
       </c>
       <c r="G10" t="n">
         <v>-0.2139</v>
@@ -1234,13 +1234,13 @@
         <v>1.7401</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.053</v>
+        <v>-0.0424</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8051</v>
+        <v>0.5384</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.8581</v>
+        <v>-0.5807</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4345</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2572</v>
+        <v>-4.0838</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9069</v>
+        <v>-1.7951</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3503</v>
+        <v>-2.2887</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5933</v>
@@ -1312,13 +1312,13 @@
         <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8169</v>
+        <v>-0.6435</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4864</v>
+        <v>-0.4248</v>
       </c>
       <c r="V11" t="n">
         <v>-1.282</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.858000000000001</v>
+        <v>-3.515500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>5.602399999999999</v>
+        <v>5.945100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-9.460699999999999</v>
+        <v>-9.460700000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>4.637700000000001</v>
+        <v>4.637699999999999</v>
       </c>
       <c r="H12" t="n">
         <v>0.1675000000000004</v>
@@ -1366,7 +1366,7 @@
         <v>13.1099</v>
       </c>
       <c r="K12" t="n">
-        <v>7.8185</v>
+        <v>7.818499999999998</v>
       </c>
       <c r="L12" t="n">
         <v>5.2913</v>
@@ -1375,13 +1375,13 @@
         <v>-8.472099999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.6512</v>
+        <v>-7.651199999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-0.8209</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.999999999993348e-05</v>
+        <v>-9.999999999971143e-05</v>
       </c>
       <c r="Q12" t="n">
         <v>-11.9628</v>
@@ -1390,22 +1390,22 @@
         <v>11.9628</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.5173</v>
+        <v>-2.1751</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0034</v>
+        <v>1.3459</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.521</v>
+        <v>-3.520999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.978300000000001</v>
+        <v>-5.9783</v>
       </c>
       <c r="W12" t="n">
         <v>3.452</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.430100000000001</v>
+        <v>-9.430099999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.0464</v>
+        <v>4.4401</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3106</v>
+        <v>4.8636</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2642</v>
+        <v>-0.4234</v>
       </c>
       <c r="G13" t="n">
         <v>3.3673</v>
@@ -1468,13 +1468,13 @@
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>1.269</v>
+        <v>0.6627</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9542</v>
+        <v>0.5071</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3148</v>
+        <v>0.1556</v>
       </c>
       <c r="V13" t="n">
         <v>3.0202</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SOLA IDDRISU</t>
+          <t>V. ARTEAGA GONZALEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6325</v>
+        <v>3.7371</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5424</v>
+        <v>3.6939</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0901</v>
+        <v>0.0432</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.08550000000000001</v>
+        <v>2.3443</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.229</v>
+        <v>2.3419</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1435</v>
+        <v>0.0024</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2351</v>
+        <v>2.9501</v>
       </c>
       <c r="K14" t="n">
-        <v>0.2007</v>
+        <v>2.7588</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0343</v>
+        <v>0.1912</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3206</v>
+        <v>-0.6057</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4298</v>
+        <v>-0.4169</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1091</v>
+        <v>-0.1889</v>
       </c>
       <c r="P14" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4783</v>
+        <v>1.153</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5248</v>
+        <v>0.7439</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0465</v>
+        <v>0.4092</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3698</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. ARTEAGA GONZALEZ</t>
+          <t>A. SOLA IDDRISU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6152</v>
+        <v>2.4482</v>
       </c>
       <c r="E15" t="n">
-        <v>4.0292</v>
+        <v>2.4248</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.414</v>
+        <v>0.0234</v>
       </c>
       <c r="G15" t="n">
-        <v>2.3443</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3419</v>
+        <v>-1.229</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0024</v>
+        <v>1.1435</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9501</v>
+        <v>1.2351</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7588</v>
+        <v>0.2007</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1912</v>
+        <v>1.0343</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6057</v>
+        <v>-1.3206</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4169</v>
+        <v>-1.4298</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1889</v>
+        <v>0.1091</v>
       </c>
       <c r="P15" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R15" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0311</v>
+        <v>1.2939</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0791</v>
+        <v>1.4072</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0481</v>
+        <v>-0.1133</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2572</v>
+        <v>1.5597</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2138</v>
+        <v>2.3313</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9566</v>
+        <v>-0.7716</v>
       </c>
       <c r="G16" t="n">
         <v>-1.5725</v>
@@ -1702,13 +1702,13 @@
         <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1253</v>
+        <v>0.1772</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6609</v>
+        <v>0.4567</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4643</v>
+        <v>-0.2794</v>
       </c>
       <c r="V16" t="n">
         <v>3.3899</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. SCHOTT</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1791</v>
+        <v>0.3762</v>
       </c>
       <c r="E17" t="n">
-        <v>0.419</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2399</v>
+        <v>0.283</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8794</v>
+        <v>-3.034</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8212</v>
+        <v>-0.6905</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0582</v>
+        <v>-2.3436</v>
       </c>
       <c r="J17" t="n">
-        <v>0.07290000000000001</v>
+        <v>-1.1954</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6538</v>
+        <v>0.4078</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7267</v>
+        <v>-1.6032</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9523</v>
+        <v>-1.8386</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1674</v>
+        <v>-1.0983</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7849</v>
+        <v>-0.7403</v>
       </c>
       <c r="P17" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0513</v>
+        <v>0.3656</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5636</v>
+        <v>0.3761</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6149</v>
+        <v>-0.0105</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1952</v>
+        <v>1.3045</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>F. SCHOTT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1578</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1303</v>
+        <v>0.0838</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2881</v>
+        <v>-0.1474</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.034</v>
+        <v>-0.8794</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6905</v>
+        <v>-0.8212</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.3436</v>
+        <v>-0.0582</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1954</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4078</v>
+        <v>-0.6538</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.6032</v>
+        <v>0.7267</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8386</v>
+        <v>-0.9523</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0983</v>
+        <v>-0.1674</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7403</v>
+        <v>-0.7849</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.2175</v>
       </c>
       <c r="R18" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1472</v>
+        <v>-0.2941</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1526</v>
+        <v>0.2283</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0054</v>
+        <v>-0.5224</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3045</v>
+        <v>-0.1952</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1745</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5331</v>
+        <v>-0.8068</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3527</v>
+        <v>0.0174</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8858</v>
+        <v>-0.8242</v>
       </c>
       <c r="G19" t="n">
         <v>-2.2438</v>
@@ -1936,13 +1936,13 @@
         <v>0.435</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1456</v>
+        <v>-0.128</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2569</v>
+        <v>-0.1953</v>
       </c>
       <c r="V19" t="n">
         <v>1.13</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5397</v>
+        <v>-1.135</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1376</v>
+        <v>-0.5788</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4021</v>
+        <v>-0.5562</v>
       </c>
       <c r="G20" t="n">
         <v>-1.389</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1953</v>
+        <v>0.2094</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.399</v>
+        <v>0.1598</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2037</v>
+        <v>0.0496</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3904</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3288</v>
+        <v>-1.6172</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8348</v>
+        <v>-1.6113</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4939</v>
+        <v>-0.0059</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5750999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.7401</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1235</v>
+        <v>-0.4119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.5299</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.37</v>
+        <v>0.1181</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1952</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.6284</v>
+        <v>-4.3355</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3043</v>
+        <v>-1.8572</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3241</v>
+        <v>-2.4782</v>
       </c>
       <c r="G22" t="n">
         <v>-0.5701000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0583</v>
+        <v>0.2346</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3425</v>
+        <v>0.1046</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2842</v>
+        <v>0.1301</v>
       </c>
       <c r="V22" t="n">
         <v>-2.2599</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.858199999999999</v>
+        <v>4.603099999999998</v>
       </c>
       <c r="E23" t="n">
         <v>9.460700000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.602399999999999</v>
+        <v>-4.8573</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.637799999999999</v>
+        <v>-4.637799999999998</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1673000000000008</v>
+        <v>-0.1673000000000006</v>
       </c>
       <c r="I23" t="n">
         <v>-4.4703</v>
@@ -2233,7 +2233,7 @@
         <v>-13.1099</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.818600000000001</v>
+        <v>-7.818599999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-5.291399999999999</v>
@@ -2248,13 +2248,13 @@
         <v>11.9629</v>
       </c>
       <c r="S23" t="n">
-        <v>2.5175</v>
+        <v>3.2624</v>
       </c>
       <c r="T23" t="n">
-        <v>3.521</v>
+        <v>3.5211</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0034</v>
+        <v>-0.2583</v>
       </c>
       <c r="V23" t="n">
         <v>5.9785</v>
